--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1709-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1709-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEAA98FE-8AA5-44BE-B01C-0331EDEBD63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7E703E5-0087-42AE-8A81-581E3FC02E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{5CA6982B-44BA-4DF1-A255-FA87E6AB45A0}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{FB1563CF-393C-4A58-9466-957423CBECC1}"/>
   </bookViews>
   <sheets>
     <sheet name="1709-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1451,23 +1451,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DBA55B-7F49-45B9-8AA3-9BC371E4F13A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1F68199-2E64-41CD-8DD4-79FD8F9AFB74}">
   <dimension ref="A1:R56"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1495,7 +1494,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1525,7 +1524,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1571,7 +1570,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1621,7 +1620,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1675,7 +1674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1731,7 +1730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1785,7 +1784,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1841,7 +1840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1897,7 +1896,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1953,7 +1952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2024</v>
       </c>
@@ -2007,7 +2006,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2063,7 +2062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2119,7 +2118,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2023</v>
       </c>
@@ -2173,7 +2172,7 @@
         <v>7.53</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2229,7 +2228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2285,7 +2284,7 @@
         <v>7.53</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2022</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2021</v>
       </c>
@@ -2393,7 +2392,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="38">
         <v>2020</v>
       </c>
@@ -2447,7 +2446,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2019</v>
       </c>
@@ -2501,7 +2500,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2018</v>
       </c>
@@ -2555,7 +2554,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2017</v>
       </c>
@@ -2609,7 +2608,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2016</v>
       </c>
@@ -2663,7 +2662,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2015</v>
       </c>
@@ -2717,7 +2716,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2014</v>
       </c>
@@ -2771,7 +2770,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2013</v>
       </c>
@@ -2825,7 +2824,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2012</v>
       </c>
@@ -2879,7 +2878,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2011</v>
       </c>
@@ -2933,7 +2932,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2010</v>
       </c>
@@ -2987,7 +2986,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2009</v>
       </c>
@@ -3041,7 +3040,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2008</v>
       </c>
@@ -3095,7 +3094,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2007</v>
       </c>
@@ -3149,7 +3148,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2006</v>
       </c>
@@ -3203,7 +3202,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2005</v>
       </c>
@@ -3257,7 +3256,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2004</v>
       </c>
@@ -3311,7 +3310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2003</v>
       </c>
@@ -3365,7 +3364,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2002</v>
       </c>
@@ -3419,7 +3418,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2001</v>
       </c>
@@ -3473,7 +3472,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>2000</v>
       </c>
@@ -3527,7 +3526,7 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>1999</v>
       </c>
@@ -3581,7 +3580,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>1998</v>
       </c>
@@ -3635,7 +3634,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>1997</v>
       </c>
@@ -3689,7 +3688,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>1996</v>
       </c>
@@ -3743,7 +3742,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>1995</v>
       </c>
@@ -3797,7 +3796,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>1994</v>
       </c>
@@ -3851,7 +3850,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40">
         <v>1993</v>
       </c>
@@ -3905,7 +3904,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="38">
         <v>1992</v>
       </c>
@@ -3959,7 +3958,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
         <v>1991</v>
       </c>
@@ -4013,7 +4012,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>1990</v>
       </c>
@@ -4067,7 +4066,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="40">
         <v>1989</v>
       </c>
@@ -4121,7 +4120,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="38">
         <v>1988</v>
       </c>
@@ -4175,7 +4174,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="40">
         <v>1987</v>
       </c>
@@ -4229,7 +4228,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="38">
         <v>1986</v>
       </c>
@@ -4283,7 +4282,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="40">
         <v>1985</v>
       </c>
@@ -4337,7 +4336,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="38">
         <v>1984</v>
       </c>
@@ -4391,7 +4390,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="40" t="s">
         <v>35</v>
       </c>
